--- a/Business Analysis/1.+Trend+analysis_before.xlsx
+++ b/Business Analysis/1.+Trend+analysis_before.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Courses\Video creating\Enterprise excellence\Case study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\Financial-Analysis\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CDFDAA-0DC1-45F3-90F3-96E5B578DE2A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB691CC2-262A-44C3-A940-E19BF282DE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{F12A9117-8F43-4D89-91AA-57E2FEF63FB4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{F12A9117-8F43-4D89-91AA-57E2FEF63FB4}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="1" r:id="rId1"/>
@@ -198,13 +198,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -235,6 +234,1432 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1100">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>Revenue</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" sz="1100" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="002060"/>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> Trend Analysis 2019-2021</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN" sz="1100">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.8888985423654406E-2"/>
+          <c:y val="3.4026470093099462E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1. Trend analysis'!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Revenue</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="002060"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'1. Trend analysis'!$C$4:$AL$4</c:f>
+              <c:numCache>
+                <c:formatCode>[$-409]mmm\-yy;@</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>43496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43524</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43555</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43585</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43616</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43646</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43677</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43708</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>43738</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>43769</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43799</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>43830</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>43861</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43890</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>43921</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>43951</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43982</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44043</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44074</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44104</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44135</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44165</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44196</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44227</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44255</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>44286</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44316</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>44347</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44377</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44408</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44439</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>44469</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>44500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44530</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>44561</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1. Trend analysis'!$C$5:$AL$5</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>1941.2307692307691</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1849.4690780228509</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2175.2769230769227</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2080.8114935648005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2249.1230769230765</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2268.6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2498.3076923076919</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1462.7392706420908</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2334.9230769230767</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2639.8615413642956</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2258.8321142992068</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2448.0830535688224</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2660.0985011616999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2301.820609688868</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2545.2376374103087</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2850.2724207650704</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3038.4310200419095</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3081.4457503043245</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3239.2990697390751</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1844.6118688762529</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2926.9243830603632</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3382.5564278401821</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3102.5376031076216</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2853.3720012781246</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3363.3852773606832</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2896.4020535350955</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3365.879258708992</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3715.4704340513654</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4039.0341221931335</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>3971.8638408805</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4245.9215971449739</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2486.2807465538858</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3863.1103827011807</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4289.1516580473954</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4193.7394584541544</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3799.390432295012</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6B7C-43B8-9E36-AFBE95C97A1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'1. Trend analysis'!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cogs</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'1. Trend analysis'!$C$4:$AL$4</c:f>
+              <c:numCache>
+                <c:formatCode>[$-409]mmm\-yy;@</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>43496</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43524</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43555</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43585</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43616</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43646</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43677</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43708</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>43738</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>43769</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43799</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>43830</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>43861</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>43890</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>43921</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>43951</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>43982</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44012</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>44043</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>44074</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>44104</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>44135</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>44165</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>44196</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>44227</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44255</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>44286</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>44316</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>44347</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>44377</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>44408</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>44439</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>44469</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>44500</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>44530</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>44561</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'1. Trend analysis'!$C$6:$AL$6</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="36"/>
+                <c:pt idx="0">
+                  <c:v>706.15384615384608</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>710.76923076923072</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>656.30769230769238</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>670.61538461538453</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>593.53846153846155</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>583.38461538461536</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>474.46153846153845</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>639.69230769230762</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>676.61538461538453</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>571.38461538461536</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>422.76923076923066</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>596.71949207527507</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>504.42901070568638</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>596.36058786890646</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>726.58170848780583</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>705.03445476861111</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>683.74813890747942</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>612.10540577172105</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>509.49498696850935</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>716.91889176476468</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>731.14755311591955</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>590.71973108505404</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>589.9854844016553</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>830.40526365672724</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>681.69872570104417</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>881.25703792407626</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>962.77009739234722</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>984.26685700500332</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>892.57693620058262</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>849.00258706451814</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>651.03464179819332</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>969.92134547183161</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>912.00556711908484</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>886.19585760204654</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>799.51580878156631</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6B7C-43B8-9E36-AFBE95C97A1F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1858186240"/>
+        <c:axId val="1858169920"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1858186240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="[$-409]mmm\-yy;@" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1858169920"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1858169920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1858186240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>100542</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>58207</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>5292</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>75140</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5805E373-9025-B028-811D-2BCDB18E96A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -535,23 +1960,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368FC57-6F23-4732-A5C2-167A88E5ECC4}">
   <dimension ref="B1:L148"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="1"/>
-    <col min="6" max="6" width="12.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.1796875" style="1"/>
+    <col min="4" max="4" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="1"/>
+    <col min="6" max="6" width="12.453125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="9" max="9" width="18.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,49 +1984,49 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="6">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="5">
         <v>1</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>2019</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <f>EOMONTH(DATE(C5,B5,"1"),0)</f>
         <v>43496</v>
       </c>
@@ -630,14 +2055,14 @@
         <v>69.025004250191103</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B6" s="6">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
         <v>2</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>2019</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <f>EOMONTH(DATE(C6,B6,"1"),0)</f>
         <v>43524</v>
       </c>
@@ -666,14 +2091,14 @@
         <v>57.520836875159247</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="6">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="5">
         <v>3</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>2019</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <f>EOMONTH(DATE(C7,B7,"1"),0)</f>
         <v>43555</v>
       </c>
@@ -702,14 +2127,14 @@
         <v>60.851039057917099</v>
       </c>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B8" s="6">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="5">
         <v>4</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>2019</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <f t="shared" ref="D8:D71" si="0">EOMONTH(DATE(C8,B8,"1"),0)</f>
         <v>43585</v>
       </c>
@@ -738,14 +2163,14 @@
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="6">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>2019</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <f t="shared" si="0"/>
         <v>43616</v>
       </c>
@@ -774,14 +2199,14 @@
         <v>64.960981617215637</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="6">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="5">
         <v>6</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>2019</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <f t="shared" si="0"/>
         <v>43646</v>
       </c>
@@ -810,14 +2235,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="6">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="5">
         <v>7</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>2019</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f t="shared" si="0"/>
         <v>43677</v>
       </c>
@@ -846,14 +2271,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="6">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>8</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>2019</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <f t="shared" si="0"/>
         <v>43708</v>
       </c>
@@ -882,14 +2307,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="6">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="5">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>2019</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <f t="shared" si="0"/>
         <v>43738</v>
       </c>
@@ -918,14 +2343,14 @@
         <v>71.706858378858712</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="6">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
         <v>10</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>2019</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="10">
         <f t="shared" si="0"/>
         <v>43769</v>
       </c>
@@ -954,14 +2379,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="6">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="5">
         <v>11</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>2019</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <f t="shared" si="0"/>
         <v>43799</v>
       </c>
@@ -990,14 +2415,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="6">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
         <v>12</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>2019</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="10">
         <f t="shared" si="0"/>
         <v>43830</v>
       </c>
@@ -1026,14 +2451,14 @@
         <v>68.706787320924349</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B17" s="6">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
         <v>1</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>2020</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <f t="shared" si="0"/>
         <v>43861</v>
       </c>
@@ -1062,14 +2487,14 @@
         <v>78.155624371879711</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B18" s="6">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="5">
         <v>2</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>2020</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <f t="shared" si="0"/>
         <v>43890</v>
       </c>
@@ -1098,14 +2523,14 @@
         <v>65.129686976566433</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" s="6">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="5">
         <v>3</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>2020</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <f t="shared" si="0"/>
         <v>43921</v>
       </c>
@@ -1134,14 +2559,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B20" s="6">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>4</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>2020</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
@@ -1170,14 +2595,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B21" s="6">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
         <v>5</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>2020</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <f t="shared" si="0"/>
         <v>43982</v>
       </c>
@@ -1206,14 +2631,14 @@
         <v>75.274039028579637</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="6">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="5">
         <v>6</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>2020</v>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="10">
         <f t="shared" si="0"/>
         <v>44012</v>
       </c>
@@ -1242,14 +2667,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B23" s="6">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="5">
         <v>7</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>2020</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <f t="shared" si="0"/>
         <v>44043</v>
       </c>
@@ -1278,14 +2703,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="6">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
         <v>8</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>2020</v>
       </c>
-      <c r="D24" s="11">
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
         <v>44074</v>
       </c>
@@ -1314,14 +2739,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="6">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="5">
         <v>9</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>2020</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <f t="shared" si="0"/>
         <v>44104</v>
       </c>
@@ -1350,14 +2775,14 @@
         <v>84.321941536768662</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="6">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="5">
         <v>10</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>2020</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="10">
         <f t="shared" si="0"/>
         <v>44135</v>
       </c>
@@ -1386,14 +2811,14 @@
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="6">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="5">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>2020</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <f t="shared" si="0"/>
         <v>44165</v>
       </c>
@@ -1422,14 +2847,14 @@
         <v>76.996142597335265</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="6">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
         <v>12</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>2020</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="10">
         <f t="shared" si="0"/>
         <v>44196</v>
       </c>
@@ -1458,14 +2883,14 @@
         <v>80.67956081669594</v>
       </c>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="6">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="5">
         <v>1</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>2021</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <f t="shared" si="0"/>
         <v>44227</v>
       </c>
@@ -1494,14 +2919,14 @@
         <v>101.59504890398503</v>
       </c>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="6">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B30" s="5">
         <v>2</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>2021</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
         <v>44255</v>
       </c>
@@ -1530,14 +2955,14 @@
         <v>85.647647017909222</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B31" s="6">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
         <v>3</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>2021</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <f t="shared" si="0"/>
         <v>44286</v>
       </c>
@@ -1566,14 +2991,14 @@
         <v>97.037630199114446</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B32" s="6">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="5">
         <v>4</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>2021</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="10">
         <f t="shared" si="0"/>
         <v>44316</v>
       </c>
@@ -1602,14 +3027,14 @@
         <v>98.916233982605618</v>
       </c>
     </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B33" s="6">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="5">
         <v>5</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>2021</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <f t="shared" si="0"/>
         <v>44347</v>
       </c>
@@ -1638,14 +3063,14 @@
         <v>105.802493123179</v>
       </c>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B34" s="6">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="5">
         <v>6</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>2021</v>
       </c>
-      <c r="D34" s="11">
+      <c r="D34" s="10">
         <f t="shared" si="0"/>
         <v>44377</v>
       </c>
@@ -1674,14 +3099,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="6">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
         <v>7</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>2021</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <f t="shared" si="0"/>
         <v>44408</v>
       </c>
@@ -1710,14 +3135,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B36" s="6">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B36" s="5">
         <v>8</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>2021</v>
       </c>
-      <c r="D36" s="11">
+      <c r="D36" s="10">
         <f t="shared" si="0"/>
         <v>44439</v>
       </c>
@@ -1746,14 +3171,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B37" s="6">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="5">
         <v>9</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>2021</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <f t="shared" si="0"/>
         <v>44469</v>
       </c>
@@ -1782,14 +3207,14 @@
         <v>108.699557240416</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B38" s="6">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="5">
         <v>10</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>2021</v>
       </c>
-      <c r="D38" s="11">
+      <c r="D38" s="10">
         <f t="shared" si="0"/>
         <v>44500</v>
       </c>
@@ -1818,14 +3243,14 @@
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B39" s="6">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" s="5">
         <v>11</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>2021</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <f t="shared" si="0"/>
         <v>44530</v>
       </c>
@@ -1854,14 +3279,14 @@
         <v>102.40669860582705</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B40" s="6">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="5">
         <v>12</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="5">
         <v>2021</v>
       </c>
-      <c r="D40" s="11">
+      <c r="D40" s="10">
         <f t="shared" si="0"/>
         <v>44561</v>
       </c>
@@ -1890,14 +3315,14 @@
         <v>99.258185203903267</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B41" s="6">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="5">
         <v>1</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>2019</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <f t="shared" si="0"/>
         <v>43496</v>
       </c>
@@ -1926,14 +3351,14 @@
         <v>2.9796847358460092</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B42" s="6">
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>2019</v>
       </c>
-      <c r="D42" s="11">
+      <c r="D42" s="10">
         <f t="shared" si="0"/>
         <v>43524</v>
       </c>
@@ -1962,14 +3387,14 @@
         <v>3.2088912539880092</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="6">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="5">
         <v>3</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>2019</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <f t="shared" si="0"/>
         <v>43555</v>
       </c>
@@ -1998,14 +3423,14 @@
         <v>3.7655356551900114</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B44" s="6">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="5">
         <v>4</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>2019</v>
       </c>
-      <c r="D44" s="11">
+      <c r="D44" s="10">
         <f t="shared" si="0"/>
         <v>43585</v>
       </c>
@@ -2034,14 +3459,14 @@
         <v>3.6673042902720114</v>
       </c>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B45" s="6">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
         <v>5</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>2019</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <f t="shared" si="0"/>
         <v>43616</v>
       </c>
@@ -2070,14 +3495,14 @@
         <v>4.082058942148012</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B46" s="6">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B46" s="5">
         <v>6</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>2019</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <f t="shared" si="0"/>
         <v>43646</v>
       </c>
@@ -2106,14 +3531,14 @@
         <v>4.3221800563920132</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B47" s="6">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B47" s="5">
         <v>7</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>2019</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <f t="shared" si="0"/>
         <v>43677</v>
       </c>
@@ -2142,14 +3567,14 @@
         <v>4.3549238446980123</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="6">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="5">
         <v>8</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="5">
         <v>2019</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="10">
         <f t="shared" si="0"/>
         <v>43708</v>
       </c>
@@ -2178,14 +3603,14 @@
         <v>3.0560869085600095</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B49" s="6">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
         <v>9</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="5">
         <v>2019</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <f t="shared" si="0"/>
         <v>43738</v>
       </c>
@@ -2214,14 +3639,14 @@
         <v>5.0425433991240149</v>
       </c>
     </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B50" s="6">
+    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="5">
         <v>10</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>2019</v>
       </c>
-      <c r="D50" s="11">
+      <c r="D50" s="10">
         <f t="shared" si="0"/>
         <v>43769</v>
       </c>
@@ -2250,14 +3675,14 @@
         <v>5.0425433991240149</v>
       </c>
     </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B51" s="6">
+    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B51" s="5">
         <v>11</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>2019</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <f t="shared" si="0"/>
         <v>43799</v>
       </c>
@@ -2286,14 +3711,14 @@
         <v>5.5227856276120155</v>
       </c>
     </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B52" s="6">
+    <row r="52" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
         <v>12</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="5">
         <v>2019</v>
       </c>
-      <c r="D52" s="11">
+      <c r="D52" s="10">
         <f t="shared" si="0"/>
         <v>43830</v>
       </c>
@@ -2322,14 +3747,14 @@
         <v>5.7629067418560176</v>
       </c>
     </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B53" s="6">
+    <row r="53" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="5">
         <v>1</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="5">
         <v>2020</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <f t="shared" si="0"/>
         <v>43861</v>
       </c>
@@ -2358,14 +3783,14 @@
         <v>7.2522649846028084</v>
       </c>
     </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B54" s="6">
+    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B54" s="5">
         <v>2</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="5">
         <v>2020</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <f t="shared" si="0"/>
         <v>43890</v>
       </c>
@@ -2394,14 +3819,14 @@
         <v>6.8566868945335635</v>
       </c>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B55" s="6">
+    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B55" s="5">
         <v>3</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="5">
         <v>2020</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <f t="shared" si="0"/>
         <v>43921</v>
       </c>
@@ -2430,14 +3855,14 @@
         <v>8.1884664644333505</v>
       </c>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B56" s="6">
+    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B56" s="5">
         <v>4</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="5">
         <v>2020</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <f t="shared" si="0"/>
         <v>43951</v>
       </c>
@@ -2466,14 +3891,14 @@
         <v>7.3841243479592205</v>
       </c>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B57" s="6">
+    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="5">
         <v>5</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="5">
         <v>2020</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <f t="shared" si="0"/>
         <v>43982</v>
       </c>
@@ -2502,14 +3927,14 @@
         <v>8.7950195358728571</v>
       </c>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B58" s="6">
+    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B58" s="5">
         <v>6</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="5">
         <v>2020</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <f t="shared" si="0"/>
         <v>44012</v>
       </c>
@@ -2538,14 +3963,14 @@
         <v>8.7027179815233673</v>
       </c>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B59" s="6">
+    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B59" s="5">
         <v>7</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="5">
         <v>2020</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <f t="shared" si="0"/>
         <v>44043</v>
       </c>
@@ -2574,14 +3999,14 @@
         <v>8.5840445545025919</v>
       </c>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B60" s="6">
+    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="5">
         <v>8</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="5">
         <v>2020</v>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="10">
         <f t="shared" si="0"/>
         <v>44074</v>
       </c>
@@ -2610,14 +4035,14 @@
         <v>5.907299478367376</v>
       </c>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B61" s="6">
+    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B61" s="5">
         <v>9</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="5">
         <v>2020</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <f t="shared" si="0"/>
         <v>44104</v>
       </c>
@@ -2646,14 +4071,14 @@
         <v>9.1378538805995326</v>
       </c>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B62" s="6">
+    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B62" s="5">
         <v>10</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="5">
         <v>2020</v>
       </c>
-      <c r="D62" s="11">
+      <c r="D62" s="10">
         <f t="shared" si="0"/>
         <v>44135</v>
       </c>
@@ -2682,14 +4107,14 @@
         <v>9.8630803790598129</v>
       </c>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B63" s="6">
+    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="5">
         <v>11</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="5">
         <v>2020</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <f t="shared" si="0"/>
         <v>44165</v>
       </c>
@@ -2718,14 +4143,14 @@
         <v>10.153170978443926</v>
       </c>
     </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B64" s="6">
+    <row r="64" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B64" s="5">
         <v>12</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="5">
         <v>2020</v>
       </c>
-      <c r="D64" s="11">
+      <c r="D64" s="10">
         <f t="shared" si="0"/>
         <v>44196</v>
       </c>
@@ -2754,14 +4179,14 @@
         <v>9.96856786974495</v>
       </c>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B65" s="6">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B65" s="5">
         <v>1</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="5">
         <v>2021</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <f t="shared" si="0"/>
         <v>44227</v>
       </c>
@@ -2790,14 +4215,14 @@
         <v>13.236524206212621</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B66" s="6">
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" s="5">
         <v>2</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="5">
         <v>2021</v>
       </c>
-      <c r="D66" s="11">
+      <c r="D66" s="10">
         <f t="shared" si="0"/>
         <v>44255</v>
       </c>
@@ -2826,14 +4251,14 @@
         <v>11.821102698850286</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B67" s="6">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" s="5">
         <v>3</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="5">
         <v>2021</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <f t="shared" si="0"/>
         <v>44286</v>
       </c>
@@ -2862,14 +4287,14 @@
         <v>13.345402783702031</v>
       </c>
     </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B68" s="6">
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" s="5">
         <v>4</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="5">
         <v>2021</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="10">
         <f t="shared" si="0"/>
         <v>44316</v>
       </c>
@@ -2898,14 +4323,14 @@
         <v>13.065429298729258</v>
       </c>
     </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B69" s="6">
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B69" s="5">
         <v>5</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="5">
         <v>2021</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <f t="shared" si="0"/>
         <v>44347</v>
       </c>
@@ -2934,14 +4359,14 @@
         <v>14.667499796073445</v>
       </c>
     </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B70" s="6">
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="5">
         <v>6</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="5">
         <v>2021</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="10">
         <f t="shared" si="0"/>
         <v>44377</v>
       </c>
@@ -2970,14 +4395,14 @@
         <v>13.718700763665721</v>
       </c>
     </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B71" s="6">
+    <row r="71" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B71" s="5">
         <v>7</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="5">
         <v>2021</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <f t="shared" si="0"/>
         <v>44408</v>
       </c>
@@ -3006,14 +4431,14 @@
         <v>14.714162043568905</v>
       </c>
     </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B72" s="6">
+    <row r="72" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B72" s="5">
         <v>8</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="5">
         <v>2021</v>
       </c>
-      <c r="D72" s="11">
+      <c r="D72" s="10">
         <f t="shared" ref="D72:D135" si="1">EOMONTH(DATE(C72,B72,"1"),0)</f>
         <v>44439</v>
       </c>
@@ -3042,14 +4467,14 @@
         <v>9.5813148190681225</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B73" s="6">
+    <row r="73" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B73" s="5">
         <v>9</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="5">
         <v>2021</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <f t="shared" si="1"/>
         <v>44469</v>
       </c>
@@ -3078,14 +4503,14 @@
         <v>13.998674248638491</v>
       </c>
     </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B74" s="6">
+    <row r="74" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B74" s="5">
         <v>10</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="5">
         <v>2021</v>
       </c>
-      <c r="D74" s="11">
+      <c r="D74" s="10">
         <f t="shared" si="1"/>
         <v>44500</v>
       </c>
@@ -3114,14 +4539,14 @@
         <v>16.45621928339947</v>
       </c>
     </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B75" s="6">
+    <row r="75" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B75" s="5">
         <v>11</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="5">
         <v>2021</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <f t="shared" si="1"/>
         <v>44530</v>
       </c>
@@ -3150,14 +4575,14 @@
         <v>16.082921303435779</v>
       </c>
     </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B76" s="6">
+    <row r="76" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B76" s="5">
         <v>12</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="5">
         <v>2021</v>
       </c>
-      <c r="D76" s="11">
+      <c r="D76" s="10">
         <f t="shared" si="1"/>
         <v>44561</v>
       </c>
@@ -3186,14 +4611,14 @@
         <v>15.678515158475117</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B77" s="6">
+    <row r="77" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B77" s="5">
         <v>1</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="5">
         <v>2019</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <f t="shared" si="1"/>
         <v>43496</v>
       </c>
@@ -3222,14 +4647,14 @@
         <v>2.5124397260372198</v>
       </c>
     </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B78" s="6">
+    <row r="78" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B78" s="5">
         <v>2</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="5">
         <v>2019</v>
       </c>
-      <c r="D78" s="11">
+      <c r="D78" s="10">
         <f t="shared" si="1"/>
         <v>43524</v>
       </c>
@@ -3258,14 +4683,14 @@
         <v>2.7057043203477753</v>
       </c>
     </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B79" s="6">
+    <row r="79" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B79" s="5">
         <v>3</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="5">
         <v>2019</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <f t="shared" si="1"/>
         <v>43555</v>
       </c>
@@ -3294,14 +4719,14 @@
         <v>3.1750611922448386</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B80" s="6">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B80" s="5">
         <v>4</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="5">
         <v>2019</v>
       </c>
-      <c r="D80" s="11">
+      <c r="D80" s="10">
         <f t="shared" si="1"/>
         <v>43585</v>
       </c>
@@ -3330,14 +4755,14 @@
         <v>3.0922335089688859</v>
       </c>
     </row>
-    <row r="81" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B81" s="6">
+    <row r="81" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B81" s="5">
         <v>5</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="5">
         <v>2019</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <f t="shared" si="1"/>
         <v>43616</v>
       </c>
@@ -3366,14 +4791,14 @@
         <v>3.4419503939117955</v>
       </c>
     </row>
-    <row r="82" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B82" s="6">
+    <row r="82" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B82" s="5">
         <v>6</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="5">
         <v>2019</v>
       </c>
-      <c r="D82" s="11">
+      <c r="D82" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
       </c>
@@ -3402,14 +4827,14 @@
         <v>3.6444180641419015</v>
       </c>
     </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B83" s="6">
+    <row r="83" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B83" s="5">
         <v>7</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="5">
         <v>2019</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <f t="shared" si="1"/>
         <v>43677</v>
       </c>
@@ -3438,14 +4863,14 @@
         <v>3.6720272919005521</v>
       </c>
     </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B84" s="6">
+    <row r="84" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B84" s="5">
         <v>8</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="5">
         <v>2019</v>
       </c>
-      <c r="D84" s="11">
+      <c r="D84" s="10">
         <f t="shared" si="1"/>
         <v>43708</v>
       </c>
@@ -3474,14 +4899,14 @@
         <v>2.5768612574740724</v>
       </c>
     </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B85" s="6">
+    <row r="85" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B85" s="5">
         <v>9</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="5">
         <v>2019</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <f t="shared" si="1"/>
         <v>43738</v>
       </c>
@@ -3510,14 +4935,14 @@
         <v>4.2518210748322174</v>
       </c>
     </row>
-    <row r="86" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B86" s="6">
+    <row r="86" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B86" s="5">
         <v>10</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="5">
         <v>2019</v>
       </c>
-      <c r="D86" s="11">
+      <c r="D86" s="10">
         <f t="shared" si="1"/>
         <v>43769</v>
       </c>
@@ -3546,14 +4971,14 @@
         <v>4.2518210748322174</v>
       </c>
     </row>
-    <row r="87" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B87" s="6">
+    <row r="87" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B87" s="5">
         <v>11</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="5">
         <v>2019</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <f t="shared" si="1"/>
         <v>43799</v>
       </c>
@@ -3582,14 +5007,14 @@
         <v>4.6567564152924295</v>
       </c>
     </row>
-    <row r="88" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B88" s="6">
+    <row r="88" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B88" s="5">
         <v>12</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="5">
         <v>2019</v>
       </c>
-      <c r="D88" s="11">
+      <c r="D88" s="10">
         <f t="shared" si="1"/>
         <v>43830</v>
       </c>
@@ -3618,14 +5043,14 @@
         <v>4.8592240855225359</v>
       </c>
     </row>
-    <row r="89" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B89" s="6">
+    <row r="89" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B89" s="5">
         <v>1</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="5">
         <v>2020</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <f t="shared" si="1"/>
         <v>43861</v>
       </c>
@@ -3654,14 +5079,14 @@
         <v>5.9873962294839496</v>
       </c>
     </row>
-    <row r="90" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B90" s="6">
+    <row r="90" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B90" s="5">
         <v>2</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="5">
         <v>2020</v>
       </c>
-      <c r="D90" s="11">
+      <c r="D90" s="10">
         <f t="shared" si="1"/>
         <v>43890</v>
       </c>
@@ -3690,14 +5115,14 @@
         <v>5.6608109806030038</v>
       </c>
     </row>
-    <row r="91" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B91" s="6">
+    <row r="91" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B91" s="5">
         <v>3</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="5">
         <v>2020</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <f t="shared" si="1"/>
         <v>43921</v>
       </c>
@@ -3726,14 +5151,14 @@
         <v>6.7603146518355102</v>
       </c>
     </row>
-    <row r="92" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B92" s="6">
+    <row r="92" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B92" s="5">
         <v>4</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="5">
         <v>2020</v>
       </c>
-      <c r="D92" s="11">
+      <c r="D92" s="10">
         <f t="shared" si="1"/>
         <v>43951</v>
       </c>
@@ -3762,14 +5187,14 @@
         <v>6.0962579791109262</v>
       </c>
     </row>
-    <row r="93" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B93" s="6">
+    <row r="93" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B93" s="5">
         <v>5</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="5">
         <v>2020</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
       </c>
@@ -3798,14 +5223,14 @@
         <v>7.2610787001196222</v>
       </c>
     </row>
-    <row r="94" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B94" s="6">
+    <row r="94" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B94" s="5">
         <v>6</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="5">
         <v>2020</v>
       </c>
-      <c r="D94" s="11">
+      <c r="D94" s="10">
         <f t="shared" si="1"/>
         <v>44012</v>
       </c>
@@ -3834,14 +5259,14 @@
         <v>7.1848754753807356</v>
       </c>
     </row>
-    <row r="95" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B95" s="6">
+    <row r="95" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B95" s="5">
         <v>7</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="5">
         <v>2020</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <f t="shared" si="1"/>
         <v>44043</v>
       </c>
@@ -3870,14 +5295,14 @@
         <v>7.0868999007164515</v>
       </c>
     </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B96" s="6">
+    <row r="96" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B96" s="5">
         <v>8</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="5">
         <v>2020</v>
       </c>
-      <c r="D96" s="11">
+      <c r="D96" s="10">
         <f t="shared" si="1"/>
         <v>44074</v>
       </c>
@@ -3906,14 +5331,14 @@
         <v>4.8770063832887409</v>
       </c>
     </row>
-    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B97" s="6">
+    <row r="97" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B97" s="5">
         <v>9</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="5">
         <v>2020</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <f t="shared" si="1"/>
         <v>44104</v>
       </c>
@@ -3942,14 +5367,14 @@
         <v>7.5441192491497713</v>
       </c>
     </row>
-    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B98" s="6">
+    <row r="98" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B98" s="5">
         <v>10</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="5">
         <v>2020</v>
       </c>
-      <c r="D98" s="11">
+      <c r="D98" s="10">
         <f t="shared" si="1"/>
         <v>44135</v>
       </c>
@@ -3978,14 +5403,14 @@
         <v>8.1428588720981647</v>
       </c>
     </row>
-    <row r="99" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B99" s="6">
+    <row r="99" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B99" s="5">
         <v>11</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="5">
         <v>2020</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <f t="shared" si="1"/>
         <v>44165</v>
       </c>
@@ -4014,14 +5439,14 @@
         <v>8.382354721277526</v>
       </c>
     </row>
-    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B100" s="6">
+    <row r="100" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B100" s="5">
         <v>12</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="5">
         <v>2020</v>
       </c>
-      <c r="D100" s="11">
+      <c r="D100" s="10">
         <f t="shared" si="1"/>
         <v>44196</v>
       </c>
@@ -4050,14 +5475,14 @@
         <v>8.2299482717997527</v>
       </c>
     </row>
-    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B101" s="6">
+    <row r="101" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B101" s="5">
         <v>1</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="5">
         <v>2021</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <f t="shared" si="1"/>
         <v>44227</v>
       </c>
@@ -4086,14 +5511,14 @@
         <v>10.737220126311428</v>
       </c>
     </row>
-    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B102" s="6">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B102" s="5">
         <v>2</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="5">
         <v>2021</v>
       </c>
-      <c r="D102" s="11">
+      <c r="D102" s="10">
         <f t="shared" si="1"/>
         <v>44255</v>
       </c>
@@ -4122,14 +5547,14 @@
         <v>9.5890567520525085</v>
       </c>
     </row>
-    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B103" s="6">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="5">
         <v>3</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="5">
         <v>2021</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <f t="shared" si="1"/>
         <v>44286</v>
       </c>
@@ -4158,14 +5583,14 @@
         <v>10.825540385869804</v>
       </c>
     </row>
-    <row r="104" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B104" s="6">
+    <row r="104" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B104" s="5">
         <v>4</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="5">
         <v>2021</v>
       </c>
-      <c r="D104" s="11">
+      <c r="D104" s="10">
         <f t="shared" si="1"/>
         <v>44316</v>
       </c>
@@ -4194,14 +5619,14 @@
         <v>10.598431147005403</v>
       </c>
     </row>
-    <row r="105" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B105" s="6">
+    <row r="105" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B105" s="5">
         <v>5</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="5">
         <v>2021</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <f t="shared" si="1"/>
         <v>44347</v>
       </c>
@@ -4230,14 +5655,14 @@
         <v>11.898000680507254</v>
       </c>
     </row>
-    <row r="106" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B106" s="6">
+    <row r="106" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B106" s="5">
         <v>6</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="5">
         <v>2021</v>
       </c>
-      <c r="D106" s="11">
+      <c r="D106" s="10">
         <f t="shared" si="1"/>
         <v>44377</v>
       </c>
@@ -4266,14 +5691,14 @@
         <v>11.128352704355672</v>
       </c>
     </row>
-    <row r="107" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B107" s="6">
+    <row r="107" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B107" s="5">
         <v>7</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="5">
         <v>2021</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <f t="shared" si="1"/>
         <v>44408</v>
       </c>
@@ -4302,14 +5727,14 @@
         <v>11.935852220317987</v>
       </c>
     </row>
-    <row r="108" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B108" s="6">
+    <row r="108" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B108" s="5">
         <v>8</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="5">
         <v>2021</v>
       </c>
-      <c r="D108" s="11">
+      <c r="D108" s="10">
         <f t="shared" si="1"/>
         <v>44439</v>
       </c>
@@ -4338,14 +5763,14 @@
         <v>7.772182841137294</v>
       </c>
     </row>
-    <row r="109" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B109" s="6">
+    <row r="109" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B109" s="5">
         <v>9</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="5">
         <v>2021</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <f t="shared" si="1"/>
         <v>44469</v>
       </c>
@@ -4374,14 +5799,14 @@
         <v>11.355461943220073</v>
       </c>
     </row>
-    <row r="110" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B110" s="6">
+    <row r="110" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B110" s="5">
         <v>10</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="5">
         <v>2021</v>
       </c>
-      <c r="D110" s="11">
+      <c r="D110" s="10">
         <f t="shared" si="1"/>
         <v>44500</v>
       </c>
@@ -4410,14 +5835,14 @@
         <v>13.348976373252041</v>
       </c>
     </row>
-    <row r="111" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B111" s="6">
+    <row r="111" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B111" s="5">
         <v>11</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="5">
         <v>2021</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <f t="shared" si="1"/>
         <v>44530</v>
       </c>
@@ -4446,14 +5871,14 @@
         <v>13.046164054766171</v>
       </c>
     </row>
-    <row r="112" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B112" s="6">
+    <row r="112" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B112" s="5">
         <v>12</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="5">
         <v>2021</v>
       </c>
-      <c r="D112" s="11">
+      <c r="D112" s="10">
         <f t="shared" si="1"/>
         <v>44561</v>
       </c>
@@ -4482,14 +5907,14 @@
         <v>12.718117376406488</v>
       </c>
     </row>
-    <row r="113" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B113" s="6">
+    <row r="113" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B113" s="5">
         <v>1</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>2019</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <f t="shared" si="1"/>
         <v>43496</v>
       </c>
@@ -4518,14 +5943,14 @@
         <v>5.0927506849621826</v>
       </c>
     </row>
-    <row r="114" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B114" s="6">
+    <row r="114" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B114" s="5">
         <v>2</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="5">
         <v>2019</v>
       </c>
-      <c r="D114" s="11">
+      <c r="D114" s="10">
         <f t="shared" si="1"/>
         <v>43524</v>
       </c>
@@ -4554,14 +5979,14 @@
         <v>6.8111205198607507</v>
       </c>
     </row>
-    <row r="115" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B115" s="6">
+    <row r="115" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B115" s="5">
         <v>3</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="5">
         <v>2019</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="10">
         <f t="shared" si="1"/>
         <v>43555</v>
       </c>
@@ -4590,14 +6015,14 @@
         <v>10.312070251557737</v>
       </c>
     </row>
-    <row r="116" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B116" s="6">
+    <row r="116" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B116" s="5">
         <v>4</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="5">
         <v>2019</v>
       </c>
-      <c r="D116" s="11">
+      <c r="D116" s="10">
         <f t="shared" si="1"/>
         <v>43585</v>
       </c>
@@ -4626,14 +6051,14 @@
         <v>9.0699708680454449</v>
       </c>
     </row>
-    <row r="117" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B117" s="6">
+    <row r="117" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B117" s="5">
         <v>5</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="5">
         <v>2019</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="10">
         <f t="shared" si="1"/>
         <v>43616</v>
       </c>
@@ -4662,14 +6087,14 @@
         <v>9.2450190868322792</v>
       </c>
     </row>
-    <row r="118" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B118" s="6">
+    <row r="118" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B118" s="5">
         <v>6</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="5">
         <v>2019</v>
       </c>
-      <c r="D118" s="11">
+      <c r="D118" s="10">
         <f t="shared" si="1"/>
         <v>43646</v>
       </c>
@@ -4698,14 +6123,14 @@
         <v>9.4680150042305797</v>
       </c>
     </row>
-    <row r="119" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B119" s="6">
+    <row r="119" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B119" s="5">
         <v>7</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="5">
         <v>2019</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <f t="shared" si="1"/>
         <v>43677</v>
       </c>
@@ -4734,14 +6159,14 @@
         <v>7.4921779038167768</v>
       </c>
     </row>
-    <row r="120" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B120" s="6">
+    <row r="120" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B120" s="5">
         <v>8</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>2019</v>
       </c>
-      <c r="D120" s="11">
+      <c r="D120" s="10">
         <f t="shared" si="1"/>
         <v>43708</v>
       </c>
@@ -4770,14 +6195,14 @@
         <v>5.3109476024213489</v>
       </c>
     </row>
-    <row r="121" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B121" s="6">
+    <row r="121" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B121" s="5">
         <v>9</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>2019</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="10">
         <f t="shared" si="1"/>
         <v>43738</v>
       </c>
@@ -4806,14 +6231,14 @@
         <v>10.316668058759298</v>
       </c>
     </row>
-    <row r="122" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B122" s="6">
+    <row r="122" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B122" s="5">
         <v>10</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="5">
         <v>2019</v>
       </c>
-      <c r="D122" s="11">
+      <c r="D122" s="10">
         <f t="shared" si="1"/>
         <v>43769</v>
       </c>
@@ -4842,14 +6267,14 @@
         <v>11.670156305808623</v>
       </c>
     </row>
-    <row r="123" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B123" s="6">
+    <row r="123" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B123" s="5">
         <v>11</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="5">
         <v>2019</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <f t="shared" si="1"/>
         <v>43799</v>
       </c>
@@ -4878,14 +6303,14 @@
         <v>13.518131529598255</v>
       </c>
     </row>
-    <row r="124" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B124" s="6">
+    <row r="124" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B124" s="5">
         <v>12</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>2019</v>
       </c>
-      <c r="D124" s="11">
+      <c r="D124" s="10">
         <f t="shared" si="1"/>
         <v>43830</v>
       </c>
@@ -4914,14 +6339,14 @@
         <v>9.2735534923399623</v>
       </c>
     </row>
-    <row r="125" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B125" s="6">
+    <row r="125" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B125" s="5">
         <v>1</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="5">
         <v>2020</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="10">
         <f t="shared" si="1"/>
         <v>43861</v>
       </c>
@@ -4950,14 +6375,14 @@
         <v>6.7970741697009123</v>
       </c>
     </row>
-    <row r="126" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B126" s="6">
+    <row r="126" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B126" s="5">
         <v>2</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="5">
         <v>2020</v>
       </c>
-      <c r="D126" s="11">
+      <c r="D126" s="10">
         <f t="shared" si="1"/>
         <v>43890</v>
       </c>
@@ -4986,14 +6411,14 @@
         <v>7.8578934918565615</v>
       </c>
     </row>
-    <row r="127" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B127" s="6">
+    <row r="127" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B127" s="5">
         <v>3</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="5">
         <v>2020</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="10">
         <f t="shared" si="1"/>
         <v>43921</v>
       </c>
@@ -5022,14 +6447,14 @@
         <v>12.641561343069679</v>
       </c>
     </row>
-    <row r="128" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B128" s="6">
+    <row r="128" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B128" s="5">
         <v>4</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="5">
         <v>2020</v>
       </c>
-      <c r="D128" s="11">
+      <c r="D128" s="10">
         <f t="shared" si="1"/>
         <v>43951</v>
       </c>
@@ -5058,14 +6483,14 @@
         <v>10.568561460047512</v>
       </c>
     </row>
-    <row r="129" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B129" s="6">
+    <row r="129" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B129" s="5">
         <v>5</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="5">
         <v>2020</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="10">
         <f t="shared" si="1"/>
         <v>43982</v>
       </c>
@@ -5094,14 +6519,14 @@
         <v>11.784181002365107</v>
       </c>
     </row>
-    <row r="130" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B130" s="6">
+    <row r="130" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B130" s="5">
         <v>6</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="5">
         <v>2020</v>
       </c>
-      <c r="D130" s="11">
+      <c r="D130" s="10">
         <f t="shared" si="1"/>
         <v>44012</v>
       </c>
@@ -5130,14 +6555,14 @@
         <v>11.50460052489913</v>
       </c>
     </row>
-    <row r="131" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B131" s="6">
+    <row r="131" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B131" s="5">
         <v>7</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="5">
         <v>2020</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="10">
         <f t="shared" si="1"/>
         <v>44043</v>
       </c>
@@ -5166,14 +6591,14 @@
         <v>9.0771045199016118</v>
       </c>
     </row>
-    <row r="132" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B132" s="6">
+    <row r="132" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B132" s="5">
         <v>8</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="5">
         <v>2020</v>
       </c>
-      <c r="D132" s="11">
+      <c r="D132" s="10">
         <f t="shared" si="1"/>
         <v>44074</v>
       </c>
@@ -5202,14 +6627,14 @@
         <v>6.4156636052953733</v>
       </c>
     </row>
-    <row r="133" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B133" s="6">
+    <row r="133" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B133" s="5">
         <v>9</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="5">
         <v>2020</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <f t="shared" si="1"/>
         <v>44104</v>
       </c>
@@ -5238,14 +6663,14 @@
         <v>11.908918774645899</v>
       </c>
     </row>
-    <row r="134" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B134" s="6">
+    <row r="134" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B134" s="5">
         <v>10</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="5">
         <v>2020</v>
       </c>
-      <c r="D134" s="11">
+      <c r="D134" s="10">
         <f t="shared" si="1"/>
         <v>44135</v>
       </c>
@@ -5274,14 +6699,14 @@
         <v>14.53319806860838</v>
       </c>
     </row>
-    <row r="135" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B135" s="6">
+    <row r="135" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B135" s="5">
         <v>11</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="5">
         <v>2020</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="10">
         <f t="shared" si="1"/>
         <v>44165</v>
       </c>
@@ -5310,14 +6735,14 @@
         <v>16.188214233067796</v>
       </c>
     </row>
-    <row r="136" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B136" s="6">
+    <row r="136" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B136" s="5">
         <v>12</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="5">
         <v>2020</v>
       </c>
-      <c r="D136" s="11">
+      <c r="D136" s="10">
         <f t="shared" ref="D136:D148" si="2">EOMONTH(DATE(C136,B136,"1"),0)</f>
         <v>44196</v>
       </c>
@@ -5346,14 +6771,14 @@
         <v>10.555823944863995</v>
       </c>
     </row>
-    <row r="137" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B137" s="6">
+    <row r="137" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B137" s="5">
         <v>1</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="5">
         <v>2021</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="10">
         <f t="shared" si="2"/>
         <v>44227</v>
       </c>
@@ -5382,14 +6807,14 @@
         <v>8.5315813046451812</v>
       </c>
     </row>
-    <row r="138" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B138" s="6">
+    <row r="138" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B138" s="5">
         <v>2</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="5">
         <v>2021</v>
       </c>
-      <c r="D138" s="11">
+      <c r="D138" s="10">
         <f t="shared" si="2"/>
         <v>44255</v>
       </c>
@@ -5418,14 +6843,14 @@
         <v>9.1851774604645069</v>
       </c>
     </row>
-    <row r="139" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B139" s="6">
+    <row r="139" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B139" s="5">
         <v>3</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="5">
         <v>2021</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="10">
         <f t="shared" si="2"/>
         <v>44286</v>
       </c>
@@ -5454,14 +6879,14 @@
         <v>14.20201699623775</v>
       </c>
     </row>
-    <row r="140" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B140" s="6">
+    <row r="140" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B140" s="5">
         <v>4</v>
       </c>
-      <c r="C140" s="6">
+      <c r="C140" s="5">
         <v>2021</v>
       </c>
-      <c r="D140" s="11">
+      <c r="D140" s="10">
         <f t="shared" si="2"/>
         <v>44316</v>
       </c>
@@ -5490,14 +6915,14 @@
         <v>13.011753250517556</v>
       </c>
     </row>
-    <row r="141" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B141" s="6">
+    <row r="141" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B141" s="5">
         <v>5</v>
       </c>
-      <c r="C141" s="6">
+      <c r="C141" s="5">
         <v>2021</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="10">
         <f t="shared" si="2"/>
         <v>44347</v>
       </c>
@@ -5526,14 +6951,14 @@
         <v>13.859429457000086</v>
       </c>
     </row>
-    <row r="142" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B142" s="6">
+    <row r="142" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B142" s="5">
         <v>6</v>
       </c>
-      <c r="C142" s="6">
+      <c r="C142" s="5">
         <v>2021</v>
       </c>
-      <c r="D142" s="11">
+      <c r="D142" s="10">
         <f t="shared" si="2"/>
         <v>44377</v>
       </c>
@@ -5562,14 +6987,14 @@
         <v>12.948386515999688</v>
       </c>
     </row>
-    <row r="143" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B143" s="6">
+    <row r="143" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B143" s="5">
         <v>7</v>
       </c>
-      <c r="C143" s="6">
+      <c r="C143" s="5">
         <v>2021</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <f t="shared" si="2"/>
         <v>44408</v>
       </c>
@@ -5598,14 +7023,14 @@
         <v>11.330204485253018</v>
       </c>
     </row>
-    <row r="144" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B144" s="6">
+    <row r="144" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B144" s="5">
         <v>8</v>
       </c>
-      <c r="C144" s="6">
+      <c r="C144" s="5">
         <v>2021</v>
       </c>
-      <c r="D144" s="11">
+      <c r="D144" s="10">
         <f t="shared" si="2"/>
         <v>44439</v>
       </c>
@@ -5634,14 +7059,14 @@
         <v>7.5916501755334727</v>
       </c>
     </row>
-    <row r="145" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B145" s="6">
+    <row r="145" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B145" s="5">
         <v>9</v>
       </c>
-      <c r="C145" s="6">
+      <c r="C145" s="5">
         <v>2021</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="10">
         <f t="shared" si="2"/>
         <v>44469</v>
       </c>
@@ -5670,14 +7095,14 @@
         <v>13.506881481661727</v>
       </c>
     </row>
-    <row r="146" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B146" s="6">
+    <row r="146" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B146" s="5">
         <v>10</v>
       </c>
-      <c r="C146" s="6">
+      <c r="C146" s="5">
         <v>2021</v>
       </c>
-      <c r="D146" s="11">
+      <c r="D146" s="10">
         <f t="shared" si="2"/>
         <v>44500</v>
       </c>
@@ -5706,14 +7131,14 @@
         <v>17.881562291072846</v>
       </c>
     </row>
-    <row r="147" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B147" s="6">
+    <row r="147" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B147" s="5">
         <v>11</v>
       </c>
-      <c r="C147" s="6">
+      <c r="C147" s="5">
         <v>2021</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="10">
         <f t="shared" si="2"/>
         <v>44530</v>
       </c>
@@ -5742,14 +7167,14 @@
         <v>19.271987850792122</v>
       </c>
     </row>
-    <row r="148" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B148" s="6">
+    <row r="148" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B148" s="5">
         <v>12</v>
       </c>
-      <c r="C148" s="6">
+      <c r="C148" s="5">
         <v>2021</v>
       </c>
-      <c r="D148" s="11">
+      <c r="D148" s="10">
         <f t="shared" si="2"/>
         <v>44561</v>
       </c>
@@ -5787,14 +7212,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D5AA4B-FF51-4BA2-8284-F92416F83C9C}">
   <dimension ref="B15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" style="7" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="2" style="6" customWidth="1"/>
+    <col min="2" max="16384" width="9.1796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="15" spans="2:2" ht="50.25" x14ac:dyDescent="0.7">
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="2:2" ht="50.5" x14ac:dyDescent="1">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -5806,249 +7231,462 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C5616EF-DC02-46F5-A8BF-BCC45ED435AB}">
-  <dimension ref="B1:AN6"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:AL6"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="1"/>
+    <col min="3" max="3" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="2" style="1" customWidth="1"/>
-    <col min="16" max="16" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="2" style="1" customWidth="1"/>
-    <col min="29" max="30" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="11" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="6.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="6.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.1796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:40" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:38" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="4" spans="2:40" ht="12.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="2:38" ht="12" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>43496</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>43524</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="11">
         <v>43555</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <v>43585</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>43616</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>43646</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>43677</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>43708</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <v>43738</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <v>43769</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <v>43799</v>
       </c>
-      <c r="N4" s="12">
+      <c r="N4" s="11">
         <v>43830</v>
       </c>
-      <c r="P4" s="12">
+      <c r="O4" s="11">
         <v>43861</v>
       </c>
-      <c r="Q4" s="12">
+      <c r="P4" s="11">
         <v>43890</v>
       </c>
-      <c r="R4" s="12">
+      <c r="Q4" s="11">
         <v>43921</v>
       </c>
-      <c r="S4" s="12">
+      <c r="R4" s="11">
         <v>43951</v>
       </c>
-      <c r="T4" s="12">
+      <c r="S4" s="11">
         <v>43982</v>
       </c>
-      <c r="U4" s="12">
+      <c r="T4" s="11">
         <v>44012</v>
       </c>
-      <c r="V4" s="12">
+      <c r="U4" s="11">
         <v>44043</v>
       </c>
-      <c r="W4" s="12">
+      <c r="V4" s="11">
         <v>44074</v>
       </c>
-      <c r="X4" s="12">
+      <c r="W4" s="11">
         <v>44104</v>
       </c>
-      <c r="Y4" s="12">
+      <c r="X4" s="11">
         <v>44135</v>
       </c>
-      <c r="Z4" s="12">
+      <c r="Y4" s="11">
         <v>44165</v>
       </c>
-      <c r="AA4" s="12">
+      <c r="Z4" s="11">
         <v>44196</v>
       </c>
-      <c r="AC4" s="12">
+      <c r="AA4" s="11">
         <v>44227</v>
       </c>
-      <c r="AD4" s="12">
+      <c r="AB4" s="11">
         <v>44255</v>
       </c>
-      <c r="AE4" s="12">
+      <c r="AC4" s="11">
         <v>44286</v>
       </c>
-      <c r="AF4" s="12">
+      <c r="AD4" s="11">
         <v>44316</v>
       </c>
-      <c r="AG4" s="12">
+      <c r="AE4" s="11">
         <v>44347</v>
       </c>
-      <c r="AH4" s="12">
+      <c r="AF4" s="11">
         <v>44377</v>
       </c>
-      <c r="AI4" s="12">
+      <c r="AG4" s="11">
         <v>44408</v>
       </c>
-      <c r="AJ4" s="12">
+      <c r="AH4" s="11">
         <v>44439</v>
       </c>
-      <c r="AK4" s="12">
+      <c r="AI4" s="11">
         <v>44469</v>
       </c>
-      <c r="AL4" s="12">
+      <c r="AJ4" s="11">
         <v>44500</v>
       </c>
-      <c r="AM4" s="12">
+      <c r="AK4" s="11">
         <v>44530</v>
       </c>
-      <c r="AN4" s="12">
+      <c r="AL4" s="11">
         <v>44561</v>
       </c>
     </row>
-    <row r="5" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="13"/>
-      <c r="AN5" s="13"/>
-    </row>
-    <row r="6" spans="2:40" x14ac:dyDescent="0.2">
+      <c r="C5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!C$4,Database!$F:$F)</f>
+        <v>1941.2307692307691</v>
+      </c>
+      <c r="D5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!D$4,Database!$F:$F)</f>
+        <v>1849.4690780228509</v>
+      </c>
+      <c r="E5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!E$4,Database!$F:$F)</f>
+        <v>2175.2769230769227</v>
+      </c>
+      <c r="F5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!F$4,Database!$F:$F)</f>
+        <v>2080.8114935648005</v>
+      </c>
+      <c r="G5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!G$4,Database!$F:$F)</f>
+        <v>2249.1230769230765</v>
+      </c>
+      <c r="H5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!H$4,Database!$F:$F)</f>
+        <v>2268.6</v>
+      </c>
+      <c r="I5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!I$4,Database!$F:$F)</f>
+        <v>2498.3076923076919</v>
+      </c>
+      <c r="J5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!J$4,Database!$F:$F)</f>
+        <v>1462.7392706420908</v>
+      </c>
+      <c r="K5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!K$4,Database!$F:$F)</f>
+        <v>2334.9230769230767</v>
+      </c>
+      <c r="L5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!L$4,Database!$F:$F)</f>
+        <v>2639.8615413642956</v>
+      </c>
+      <c r="M5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!M$4,Database!$F:$F)</f>
+        <v>2258.8321142992068</v>
+      </c>
+      <c r="N5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!N$4,Database!$F:$F)</f>
+        <v>2448.0830535688224</v>
+      </c>
+      <c r="O5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!O$4,Database!$F:$F)</f>
+        <v>2660.0985011616999</v>
+      </c>
+      <c r="P5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!P$4,Database!$F:$F)</f>
+        <v>2301.820609688868</v>
+      </c>
+      <c r="Q5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Q$4,Database!$F:$F)</f>
+        <v>2545.2376374103087</v>
+      </c>
+      <c r="R5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!R$4,Database!$F:$F)</f>
+        <v>2850.2724207650704</v>
+      </c>
+      <c r="S5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!S$4,Database!$F:$F)</f>
+        <v>3038.4310200419095</v>
+      </c>
+      <c r="T5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!T$4,Database!$F:$F)</f>
+        <v>3081.4457503043245</v>
+      </c>
+      <c r="U5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!U$4,Database!$F:$F)</f>
+        <v>3239.2990697390751</v>
+      </c>
+      <c r="V5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!V$4,Database!$F:$F)</f>
+        <v>1844.6118688762529</v>
+      </c>
+      <c r="W5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!W$4,Database!$F:$F)</f>
+        <v>2926.9243830603632</v>
+      </c>
+      <c r="X5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!X$4,Database!$F:$F)</f>
+        <v>3382.5564278401821</v>
+      </c>
+      <c r="Y5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Y$4,Database!$F:$F)</f>
+        <v>3102.5376031076216</v>
+      </c>
+      <c r="Z5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!Z$4,Database!$F:$F)</f>
+        <v>2853.3720012781246</v>
+      </c>
+      <c r="AA5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AA$4,Database!$F:$F)</f>
+        <v>3363.3852773606832</v>
+      </c>
+      <c r="AB5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AB$4,Database!$F:$F)</f>
+        <v>2896.4020535350955</v>
+      </c>
+      <c r="AC5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AC$4,Database!$F:$F)</f>
+        <v>3365.879258708992</v>
+      </c>
+      <c r="AD5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AD$4,Database!$F:$F)</f>
+        <v>3715.4704340513654</v>
+      </c>
+      <c r="AE5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AE$4,Database!$F:$F)</f>
+        <v>4039.0341221931335</v>
+      </c>
+      <c r="AF5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AF$4,Database!$F:$F)</f>
+        <v>3971.8638408805</v>
+      </c>
+      <c r="AG5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AG$4,Database!$F:$F)</f>
+        <v>4245.9215971449739</v>
+      </c>
+      <c r="AH5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AH$4,Database!$F:$F)</f>
+        <v>2486.2807465538858</v>
+      </c>
+      <c r="AI5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AI$4,Database!$F:$F)</f>
+        <v>3863.1103827011807</v>
+      </c>
+      <c r="AJ5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AJ$4,Database!$F:$F)</f>
+        <v>4289.1516580473954</v>
+      </c>
+      <c r="AK5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AK$4,Database!$F:$F)</f>
+        <v>4193.7394584541544</v>
+      </c>
+      <c r="AL5" s="12">
+        <f>SUMIF(Database!$D:$D,'1. Trend analysis'!AL$4,Database!$F:$F)</f>
+        <v>3799.390432295012</v>
+      </c>
+    </row>
+    <row r="6" spans="2:38" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
+      <c r="C6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!C$4,Database!$G:$G)</f>
+        <v>706.15384615384608</v>
+      </c>
+      <c r="D6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!D$4,Database!$G:$G)</f>
+        <v>600</v>
+      </c>
+      <c r="E6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!E$4,Database!$G:$G)</f>
+        <v>710.76923076923072</v>
+      </c>
+      <c r="F6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!F$4,Database!$G:$G)</f>
+        <v>656.30769230769238</v>
+      </c>
+      <c r="G6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!G$4,Database!$G:$G)</f>
+        <v>670.61538461538453</v>
+      </c>
+      <c r="H6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!H$4,Database!$G:$G)</f>
+        <v>593.53846153846155</v>
+      </c>
+      <c r="I6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!I$4,Database!$G:$G)</f>
+        <v>583.38461538461536</v>
+      </c>
+      <c r="J6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!J$4,Database!$G:$G)</f>
+        <v>474.46153846153845</v>
+      </c>
+      <c r="K6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!K$4,Database!$G:$G)</f>
+        <v>639.69230769230762</v>
+      </c>
+      <c r="L6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!L$4,Database!$G:$G)</f>
+        <v>676.61538461538453</v>
+      </c>
+      <c r="M6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!M$4,Database!$G:$G)</f>
+        <v>571.38461538461536</v>
+      </c>
+      <c r="N6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!N$4,Database!$G:$G)</f>
+        <v>422.76923076923066</v>
+      </c>
+      <c r="O6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!O$4,Database!$G:$G)</f>
+        <v>596.71949207527507</v>
+      </c>
+      <c r="P6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!P$4,Database!$G:$G)</f>
+        <v>504.42901070568638</v>
+      </c>
+      <c r="Q6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Q$4,Database!$G:$G)</f>
+        <v>596.36058786890646</v>
+      </c>
+      <c r="R6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!R$4,Database!$G:$G)</f>
+        <v>726.58170848780583</v>
+      </c>
+      <c r="S6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!S$4,Database!$G:$G)</f>
+        <v>705.03445476861111</v>
+      </c>
+      <c r="T6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!T$4,Database!$G:$G)</f>
+        <v>683.74813890747942</v>
+      </c>
+      <c r="U6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!U$4,Database!$G:$G)</f>
+        <v>612.10540577172105</v>
+      </c>
+      <c r="V6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!V$4,Database!$G:$G)</f>
+        <v>509.49498696850935</v>
+      </c>
+      <c r="W6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!W$4,Database!$G:$G)</f>
+        <v>716.91889176476468</v>
+      </c>
+      <c r="X6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!X$4,Database!$G:$G)</f>
+        <v>731.14755311591955</v>
+      </c>
+      <c r="Y6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Y$4,Database!$G:$G)</f>
+        <v>590.71973108505404</v>
+      </c>
+      <c r="Z6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!Z$4,Database!$G:$G)</f>
+        <v>589.9854844016553</v>
+      </c>
+      <c r="AA6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AA$4,Database!$G:$G)</f>
+        <v>830.40526365672724</v>
+      </c>
+      <c r="AB6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AB$4,Database!$G:$G)</f>
+        <v>681.69872570104417</v>
+      </c>
+      <c r="AC6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AC$4,Database!$G:$G)</f>
+        <v>881.25703792407626</v>
+      </c>
+      <c r="AD6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AD$4,Database!$G:$G)</f>
+        <v>962.77009739234722</v>
+      </c>
+      <c r="AE6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AE$4,Database!$G:$G)</f>
+        <v>984.26685700500332</v>
+      </c>
+      <c r="AF6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AF$4,Database!$G:$G)</f>
+        <v>892.57693620058262</v>
+      </c>
+      <c r="AG6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AG$4,Database!$G:$G)</f>
+        <v>849.00258706451814</v>
+      </c>
+      <c r="AH6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AH$4,Database!$G:$G)</f>
+        <v>651.03464179819332</v>
+      </c>
+      <c r="AI6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AI$4,Database!$G:$G)</f>
+        <v>969.92134547183161</v>
+      </c>
+      <c r="AJ6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AJ$4,Database!$G:$G)</f>
+        <v>912.00556711908484</v>
+      </c>
+      <c r="AK6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AK$4,Database!$G:$G)</f>
+        <v>886.19585760204654</v>
+      </c>
+      <c r="AL6" s="12">
+        <f>-SUMIF(Database!$D:$D,'1. Trend analysis'!AL$4,Database!$G:$G)</f>
+        <v>799.51580878156631</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>